--- a/branches/docs/upstream-genomics-reporting/StructureDefinition-mii-ex-molgen-familiare-linie.xlsx
+++ b/branches/docs/upstream-genomics-reporting/StructureDefinition-mii-ex-molgen-familiare-linie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T14:15:24+00:00</t>
+    <t>2026-09-02T14:33:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/docs/upstream-genomics-reporting/StructureDefinition-mii-ex-molgen-familiare-linie.xlsx
+++ b/branches/docs/upstream-genomics-reporting/StructureDefinition-mii-ex-molgen-familiare-linie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T14:33:35+00:00</t>
+    <t>2026-09-02T15:03:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/docs/upstream-genomics-reporting/StructureDefinition-mii-ex-molgen-familiare-linie.xlsx
+++ b/branches/docs/upstream-genomics-reporting/StructureDefinition-mii-ex-molgen-familiare-linie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T15:03:15+00:00</t>
+    <t>2026-09-03T06:40:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/docs/upstream-genomics-reporting/StructureDefinition-mii-ex-molgen-familiare-linie.xlsx
+++ b/branches/docs/upstream-genomics-reporting/StructureDefinition-mii-ex-molgen-familiare-linie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T06:40:42+00:00</t>
+    <t>2026-09-03T06:57:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/docs/upstream-genomics-reporting/StructureDefinition-mii-ex-molgen-familiare-linie.xlsx
+++ b/branches/docs/upstream-genomics-reporting/StructureDefinition-mii-ex-molgen-familiare-linie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T06:57:15+00:00</t>
+    <t>2026-09-03T07:38:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/docs/upstream-genomics-reporting/StructureDefinition-mii-ex-molgen-familiare-linie.xlsx
+++ b/branches/docs/upstream-genomics-reporting/StructureDefinition-mii-ex-molgen-familiare-linie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T07:38:27+00:00</t>
+    <t>2026-09-03T07:56:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/docs/upstream-genomics-reporting/StructureDefinition-mii-ex-molgen-familiare-linie.xlsx
+++ b/branches/docs/upstream-genomics-reporting/StructureDefinition-mii-ex-molgen-familiare-linie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T07:56:27+00:00</t>
+    <t>2026-09-03T08:11:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/docs/upstream-genomics-reporting/StructureDefinition-mii-ex-molgen-familiare-linie.xlsx
+++ b/branches/docs/upstream-genomics-reporting/StructureDefinition-mii-ex-molgen-familiare-linie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T08:11:50+00:00</t>
+    <t>2026-09-03T08:25:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
